--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_926_Canada_East_Coast.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_926_Canada_East_Coast.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R6cc9b0fd35454724"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rda102d32d25c4bcf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R66fa8e6d76bb47ed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Ra9d8e4d46d164faa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R70fea87d66114878"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rd34b1c35c357472b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R80b5a51cc65d4d40"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R7409f2a7559f47ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R4ea2d75e6c2a4ef0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Ra37fd0879e3643b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R174af409c4054596"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rdea07f78c6ce4217"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ926CommercialTable" displayName="EEZ926CommercialTable" ref="A1:O12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O12"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ926CommercialTable" displayName="EEZ926CommercialTable" ref="A1:E12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E12"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ926FunctionalTable" displayName="EEZ926FunctionalTable" ref="A1:O24" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O24"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ926FunctionalTable" displayName="EEZ926FunctionalTable" ref="A1:E24" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E24"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ926ValidationTable" displayName="EEZ926ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ926ValidationTable" displayName="EEZ926ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -8198,7 +8152,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R64b824699fa64a53"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R143f350762524115"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8208,20 +8162,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -8229,660 +8173,231 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>80441.86755799528</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.112757756576253</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1296.4559241772197</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>80441.86755799528</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1362.9290565788294</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$113,A2,'Species'!$U$2:$U$113))</x:f>
-        <x:v>109636558.66025765</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.112757756576253</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1296.4559241772197</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>104289335.74744228</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>5347222.912815377</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0512729597373671</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.051272959737367195</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>256854.278615331</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.3780603062790804</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>238.81428782201124</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>256854.278615331</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>340.56214945858545</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$113,A3,'Species'!$U$2:$U$113))</x:f>
-        <x:v>87474845.2228715</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.3780603062790804</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>238.81428782201124</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>61340471.62155672</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>26134373.601314776</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.4260543310223008</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.4260543310223008</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>43216.8580312095</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.07053161270326</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>1176.336608214992</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>43216.8580312095</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>1536.9518746917786</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$113,A4,'Species'!$U$2:$U$113))</x:f>
-        <x:v>66422230.96935589</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.07053161270326</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>1176.336608214992</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>50837572.19414183</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>15584658.775214061</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.3065578882425453</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.3065578882425454</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>82978.9164468747</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.3802560414502927</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>240.0247585274764</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>82978.9164468747</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>240.02635761417704</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$113,A5,'Species'!$U$2:$U$113))</x:f>
-        <x:v>19917127.073514465</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.3802560414502927</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>240.0247585274764</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>19916994.38303274</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>132.69048172608018</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0000066621739794</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.000006662173979379089</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>109591.06478108751</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.1038848994459194</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>12.702374110714842</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>109591.06478108751</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>14.519188822415096</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$113,A6,'Species'!$U$2:$U$113))</x:f>
-        <x:v>1591173.3628061344</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.1038848994459194</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>12.702374110714842</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>1392066.7040409592</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>199106.65876517515</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.1430295388771232</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.14302953887712322</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>36113.482030438005</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.2358326178821333</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>172.12050747847033</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>36113.482030438005</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>254.11249822519207</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$113,A7,'Species'!$U$2:$U$113))</x:f>
-        <x:v>9176887.138365183</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.2358326178821333</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>172.12050747847033</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>6215870.853893609</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>2961016.2844715742</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.4763638682449136</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.47636386824491367</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>7277.1721393322005</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.695909022924146</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>496.4883049650791</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>7277.1721393322005</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>782.3955565301935</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$113,A8,'Species'!$U$2:$U$113))</x:f>
-        <x:v>5693627.145918836</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.695909022924146</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>496.4883049650791</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>3613030.8603961426</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>2080596.2855226933</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.5758589854099865</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.5758589854099865</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>37927.403132366104</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.4341500336252127</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>271.73778661611414</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>37927.403132366104</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>668.8860772019796</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$113,A9,'Species'!$U$2:$U$113))</x:f>
-        <x:v>25369111.899666436</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.4341500336252127</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>271.73778661611414</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>10306308.57928624</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>15062803.320380196</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>2.461512936906782</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>1.4615129369067819</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>34044.9208522858</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.788985957959942</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>615.156982522451</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>34044.9208522858</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>616.1144286502682</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$113,A10,'Species'!$U$2:$U$113))</x:f>
-        <x:v>20975566.95934967</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.788985957959942</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>615.156982522451</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>20942970.781707805</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>32596.177641864866</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0015564256848573</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.0015564256848572462</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>4067.4871726837005</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.139647066236674</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>1379.2629371863943</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>4067.4871726837005</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>1651.555130200016</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$113,A11,'Species'!$U$2:$U$113))</x:f>
-        <x:v>6717679.307068524</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.139647066236674</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>1379.2629371863943</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>5610134.304763704</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>1107545.0023048203</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.197418625319607</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.19741862531960716</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>2411.2680664365</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.366473121812083</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>2325.2685721413523</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>2411.2680664365</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>2452.1932129913507</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$113,A12,'Species'!$U$2:$U$113))</x:f>
-        <x:v>5912895.187218362</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.366473121812083</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>2325.2685721413523</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>5606845.8538928395</x:v>
       </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>306049.33332552295</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0545849380027155</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.05458493800271547</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G12">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O12">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79868f009df548a1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b9ae54bdf3047c2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8892,20 +8407,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -8913,1308 +8418,459 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>576.531658006</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.017259172239308</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1040.5409401769998</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>576.531658006</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1110.0948443243183</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$113,A2,'Species'!$U$2:$U$113))</x:f>
-        <x:v>640004.8211422117</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.017259172239308</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1040.5409401769998</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>599904.7934633679</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>40100.02767884382</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.066843986105426</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.06684398610542601</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Jellyfish</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>216.312456292</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.4599999999999995</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>288.4031503126603</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>216.312456292</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>288.40315031266056</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$113,A3,'Species'!$U$2:$U$113))</x:f>
-        <x:v>62385.19384648249</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.4599999999999995</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>288.4031503126603</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>62385.193846482434</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>5.820766091346741e-11</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0000000000000009</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>9.330364678629499e-16</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>0.0005070181</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.69</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>489.77881936844614</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>0.0005070181</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>489.77881936844614</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$113,A4,'Species'!$U$2:$U$113))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>0.24832672641643275</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.69</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>489.77881936844614</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>0.24832672641643275</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large bathypelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>440.2573462536</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.958543975282939</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>908.9583326462293</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>440.2573462536</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>917.6283510106337</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$113,A5,'Species'!$U$2:$U$113))</x:f>
-        <x:v>403992.6226630086</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.958543975282939</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>908.9583326462293</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>400175.5833859259</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>3817.0392770826584</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.009538411226358</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.009538411226357952</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>60284.88318893559</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.121890489841889</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>1324.0076360236865</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>60284.88318893559</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>1390.9010370866315</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$113,A6,'Species'!$U$2:$U$113))</x:f>
-        <x:v>83850306.54813695</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.121890489841889</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>1324.0076360236865</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>79817645.67894669</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>4032660.869190261</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0505234254266402</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.05052342542664029</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>4844.7505043623</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.0883061501913005</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>1225.4797807209166</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>4844.7505043623</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>1753.7102976884603</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$113,A7,'Species'!$U$2:$U$113))</x:f>
-        <x:v>8496288.849231526</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.0883061501913005</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>1225.4797807209166</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>5937143.78573346</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>2559145.063498066</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.4310397652230542</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.43103976522305415</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>9074.3996556071</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1000</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>9074.3996556071</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1000.0000000000001</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$113,A8,'Species'!$U$2:$U$113))</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>9074399.6556071</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1000</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
-        <x:v>9074399.6556071</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>2496.5492448296</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.369905415416602</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>2343.7183235409034</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>2496.5492448296</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>2469.095489490989</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$113,A9,'Species'!$U$2:$U$113))</x:f>
-        <x:v>6164218.479700901</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.369905415416602</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>2343.7183235409034</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>5851208.210729338</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>313010.2689715624</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0534949804721692</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.05349498047216926</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>712.0353513054</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.8199999999999994</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>660.6934480075951</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>712.0353513054</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>660.6934480075957</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$113,A10,'Species'!$U$2:$U$113))</x:f>
-        <x:v>470437.0913572645</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.8199999999999994</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>660.6934480075951</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>470437.09135726397</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>5.238689482212067e-10</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.000000000000001</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>1.1135791752937375e-15</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>33179.8298936849</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.7846379763030393</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>609.0290048702343</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>33179.8298936849</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>611.6446171382165</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$113,A11,'Species'!$U$2:$U$113))</x:f>
-        <x:v>20294264.352034055</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.7846379763030393</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>609.0290048702343</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>20207478.78191457</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>86785.57011948526</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0042947252874097</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.004294725287409789</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>2948.0878704722004</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.25825459737012</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>1812.4022696532136</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>2948.0878704722004</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>2023.4862324788942</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$113,A12,'Species'!$U$2:$U$113))</x:f>
-        <x:v>5965415.218038519</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.25825459737012</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>1812.4022696532136</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>5343121.147580925</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>622294.0704575935</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.1164663973114917</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.1164663973114917</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>197663.0204198077</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.6101013093098344</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>407.4753198335155</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>197663.0204198077</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>430.47934613050677</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$113,A13,'Species'!$U$2:$U$113))</x:f>
-        <x:v>85089847.78449982</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.6101013093098344</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>407.4753198335155</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>80542802.46481985</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>4547045.3196799755</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0564550174631193</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.05645501746311934</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>682.2887008411</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.6021604410396986</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>400.09252830374436</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>682.2887008411</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>681.966238272106</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$113,A14,'Species'!$U$2:$U$113))</x:f>
-        <x:v>465297.85872816725</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.6021604410396986</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>400.09252830374436</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>272978.61135259276</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>192319.2473755745</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.7045213045177572</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.7045213045177572</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium bathypelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>120.3686601137</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.65</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>446.683592150963</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>120.3686601137</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>446.683592150963</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$113,A15,'Species'!$U$2:$U$113))</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>53766.70548198586</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.65</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>446.683592150963</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
-        <x:v>53766.70548198586</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>708.6941843684</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>4.067906177220482</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>1169.246765585643</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>708.6941843684</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>1359.037581348886</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$113,A16,'Species'!$U$2:$U$113))</x:f>
-        <x:v>963142.0302400519</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>4.067906177220482</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>1169.246765585643</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>828638.3828621071</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>134503.64737794478</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.162318871729512</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.1623188717295122</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>57798.15302651151</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.679928062799193</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>478.5508178694078</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>57798.15302651151</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>847.1785864464272</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$113,A17,'Species'!$U$2:$U$113))</x:f>
-        <x:v>48965357.58021431</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.679928062799193</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>478.5508178694078</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>27659353.40217827</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>21306004.178036038</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.7703001537396068</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.7703001537396068</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>88114.9377356234</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.394091328266676</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>247.79430922389216</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>88114.9377356234</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>250.37784364027578</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$113,A18,'Species'!$U$2:$U$113))</x:f>
-        <x:v>22062028.102742553</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.394091328266676</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>247.79430922389216</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>21834380.12850507</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>227647.974237483</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.0104261248955855</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.010426124895585451</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>114.4141816999</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.72</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>524.8074602497728</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>114.4141816999</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>524.8074602497728</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$113,A19,'Species'!$U$2:$U$113))</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>60045.416114480555</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.72</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>524.8074602497728</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
-        <x:v>60045.416114480555</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>112345.5052398644</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>2.1079255333729496</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>12.821107257363574</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>112345.5052398644</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>14.660006816618433</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$113,A20,'Species'!$U$2:$U$113))</x:f>
-        <x:v>1646985.872632854</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>2.1079255333729496</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>12.821107257363574</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>1440393.772563003</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>206592.10006985092</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.1434275154510323</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.14342751545103236</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>59191.2581955233</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>2.6031836282264815</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>40.103624777710856</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>59191.2581955233</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>40.29306879224342</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$113,A21,'Species'!$U$2:$U$113))</x:f>
-        <x:v>2384997.4383716625</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>2.6031836282264815</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>40.103624777710856</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>2373784.008793869</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>11213.42957779346</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.0047238626329322</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.004723862632932243</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>28862.618478411605</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.1546279486554263</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>142.76703779896553</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>28862.618478411605</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>143.60660828332988</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$113,A22,'Species'!$U$2:$U$113))</x:f>
-        <x:v>4144862.745860454</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.1546279486554263</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>142.76703779896553</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>4120630.5432845107</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>24232.202575943433</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1.005880702557873</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0.005880702557873146</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>34142.4583756024</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>4.089277539987783</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>1228.2238884789913</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>34142.4583756024</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>1679.6632123809966</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$113,A23,'Species'!$U$2:$U$113))</x:f>
-        <x:v>57347831.31374879</x:v>
-      </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>4.089277539987783</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>1228.2238884789913</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>41934582.98831449</x:v>
-      </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>15413248.325434305</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>1.367554586860429</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>0.36755458686042897</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="18" customHeight="1">
       <x:c r="A24" s="24" t="str">
         <x:v>Small to medium sharks (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B24" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C24" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D24" s="31" t="n">
+      <x:c r="B24" s="31" t="n">
         <x:v>407.3639509061</x:v>
       </x:c>
+      <x:c r="C24" s="32" t="n">
+        <x:v>3.8399999999999994</x:v>
+      </x:c>
+      <x:c r="D24" s="32" t="n">
+        <x:f>IF(C24="","",(1/'Metadata'!$B$5)^(C24-1))</x:f>
+        <x:v>691.8309709189356</x:v>
+      </x:c>
       <x:c r="E24" s="31" t="n">
-        <x:v>407.3639509061</x:v>
-      </x:c>
-      <x:c r="F24" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G24" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H24" s="32" t="n">
-        <x:f>IF(E24=0,"",I24/E24)</x:f>
-        <x:v>691.8309709189363</x:v>
-      </x:c>
-      <x:c r="I24" s="31" t="n">
-        <x:f>IF(C24=0,"",SUMIF('Species'!$G$2:$G$113,A24,'Species'!$U$2:$U$113))</x:f>
-        <x:v>281826.99767274107</x:v>
-      </x:c>
-      <x:c r="J24" s="32" t="n">
-        <x:v>3.8399999999999994</x:v>
-      </x:c>
-      <x:c r="K24" s="32" t="n">
-        <x:f>IF(J24="","",(1/'Metadata'!$B$5)^(J24-1))</x:f>
-        <x:v>691.8309709189356</x:v>
-      </x:c>
-      <x:c r="L24" s="31" t="n">
-        <x:f>IF(E24=0,"",E24*K24)</x:f>
+        <x:f>IF(B24=0,"",B24*D24)</x:f>
         <x:v>281826.9976727408</x:v>
       </x:c>
-      <x:c r="M24" s="31" t="n">
-        <x:f>IF(E24=0,"",I24-L24)</x:f>
-        <x:v>2.9103830456733704e-10</x:v>
-      </x:c>
-      <x:c r="N24" s="32" t="n">
-        <x:f>IF(L24=0,"",I24/L24)</x:f>
-        <x:v>1.000000000000001</x:v>
-      </x:c>
-      <x:c r="O24" s="34" t="n">
-        <x:f>IF(L24=0,"",M24/L24)</x:f>
-        <x:v>1.032684260098078e-15</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G24">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O24">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ef1c0d980c1492b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re63f39f9583c464c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10389,7 +9045,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -10488,7 +9144,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>358887702.9263926</x:v>
+        <x:v>290071601.88415486</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10502,7 +9158,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>358887702.9263927</x:v>
+        <x:v>309167083.59283483</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10516,7 +9172,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>-5.960464477539063e-8</x:v>
+        <x:v>-68816101.04223782</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10530,7 +9186,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-49720619.333557844</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10541,9 +9197,9 @@
         <x:v>EEZ_926</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -10555,47 +9211,19 @@
         <x:v>EEZ_926</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_926</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_926</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b7544c9385e4579"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2a3db6bdfc3f4317"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10642,7 +9270,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
